--- a/data/trans_dic/IP31KM02_R_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM02_R_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73,25%</t>
+          <t>72,79%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>63,39; 76,77</t>
+          <t>67,38; 81,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>67,59; 81,81</t>
+          <t>62,85; 76,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67,72; 78,55</t>
+          <t>67,61; 77,84</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>73,5%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>71,66%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>58,86; 72,61</t>
+          <t>67,59; 78,93</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>65,21; 77,39</t>
+          <t>63,28; 75,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64,9; 73,79</t>
+          <t>66,84; 75,22</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>56,41%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>55,91%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>29,62; 61,1</t>
+          <t>47,74; 63,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47,13; 62,15</t>
+          <t>48,5; 62,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39,39; 59,26</t>
+          <t>50,81; 61,54</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>63,46%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>57,89; 70,29</t>
+          <t>56,72; 69,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>55,57; 68,85</t>
+          <t>57,84; 71,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58,52; 67,42</t>
+          <t>58,84; 67,88</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>66,13%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>65,91%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>53,57; 66,46</t>
+          <t>63,43; 70,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62,13; 69,39</t>
+          <t>61,57; 68,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>60,07; 66,82</t>
+          <t>63,46; 68,21</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>130</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>80691</t>
+          <t>92149</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>103220</t>
+          <t>83625</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>183911</t>
+          <t>175774</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>72428; 87712</t>
+          <t>82810; 100379</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>92479; 111929</t>
+          <t>74540; 91210</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>170033; 197221</t>
+          <t>163275; 187973</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>187</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>123922</t>
+          <t>169960</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>177700</t>
+          <t>125144</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>301622</t>
+          <t>295104</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>109549; 135135</t>
+          <t>156289; 182518</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>161412; 191565</t>
+          <t>114272; 135755</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>281425; 319973</t>
+          <t>275266; 309770</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>128</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>93821</t>
+          <t>92339</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>100904</t>
+          <t>87455</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>194726</t>
+          <t>179794</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>55762; 115016</t>
+          <t>79494; 105032</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>86285; 113799</t>
+          <t>75193; 97606</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>146262; 220071</t>
+          <t>163389; 197889</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>105582</t>
+          <t>104555</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>110662</t>
+          <t>104968</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>216245</t>
+          <t>209523</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>95243; 115646</t>
+          <t>94242; 115702</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>98525; 122080</t>
+          <t>94850; 116613</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>200050; 230445</t>
+          <t>194261; 224112</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>594</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>404017</t>
+          <t>459003</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>492487</t>
+          <t>401193</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>896504</t>
+          <t>860195</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>349862; 434069</t>
+          <t>435647; 481165</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>462686; 516775</t>
+          <t>380651; 420442</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>839638; 934115</t>
+          <t>828113; 890164</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM02_R_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM02_R_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que toman una 2ª pieza de fruta diaria o verduras frescas o cocinadas más de una vez al día (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>74,98%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>70,51%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>72,79%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>67,38; 81,68</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>62,85; 76,91</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>67,61; 77,84</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>73,5%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>69,3%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>71,66%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>67,59; 78,93</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>63,28; 75,17</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>66,84; 75,22</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>55,45%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>56,41%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>55,91%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>47,74; 63,07</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>48,5; 62,96</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>50,81; 61,54</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>62,92%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>64,01%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>63,46%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>56,72; 69,63</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>57,84; 71,11</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>58,84; 67,88</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>66,83%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>64,9%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>65,91%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>63,43; 70,06</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>61,57; 68,01</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>63,46; 68,21</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.7498137365914957</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.7051124836086259</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.7278609578847951</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>92149</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>83625</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>175774</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.6738221223405741</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.6285101589577063</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.6761053133297058</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>82810; 100379</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>74540; 91210</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>163275; 187973</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.8167773358817126</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.7690726058116381</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.7783764129686058</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>426</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.7349909471961247</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.6929637468630139</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.7165616229039407</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>169960</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>125144</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>295104</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.675869298278969</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.6327599645796567</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.6683921587364313</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>156289; 182518</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>114272; 135755</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>275266; 309770</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.7892964038844911</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.7517164922886524</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.7521729462211511</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.554514509584409</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.5640890804470412</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.5591308303739406</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>92339</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>87455</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>179794</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.4773796251666674</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.4849969947401521</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.5081120617881953</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>79494; 105032</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>75193; 97606</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>163389; 197889</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.6307382494399915</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.6295612467729819</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.6154030495110607</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.6292237507873429</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.6401328372313561</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.6346421779627843</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>104555</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>104968</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>209523</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.5671585277341781</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.578426414478564</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.5884133032801548</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>94242; 115702</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>94850; 116613</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>194261; 224112</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.6963057786377769</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.7111480745309073</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.6788298994649875</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>626</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>594</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1220</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.6682978498137183</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.6489609897872654</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.659137766976775</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>459003</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>401193</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>860195</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.6342913599103251</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.6157328787664835</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.6345546466029393</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>435647; 481165</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>380651; 420442</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>828113; 890164</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.7005650024241967</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.6800986426895353</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.682101644676941</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que toman una 2ª pieza de fruta diaria o verduras frescas o cocinadas más de una vez al día (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>113</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>130</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>92149</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>83625</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>175774</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>82810</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>74540</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>163275</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>100379</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>91210</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>187973</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>239</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>187</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>169960</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>125144</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>295104</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>156289</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>114272</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>275266</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>182518</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>135755</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>309770</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>125</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>128</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>92339</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>87455</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>179794</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>79494</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>75193</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>163389</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>105032</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>97606</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>197889</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>149</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>149</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>104555</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>104968</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>209523</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>94242</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>94850</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>194261</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>115702</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>116613</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>224112</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>626</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>594</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>459003</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>401193</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>860195</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>435647</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>380651</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>828113</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>481165</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>420442</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>890164</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>